--- a/30_table/01_테스트버전/Table_Data_Mission.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Mission.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="166">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -528,6 +528,55 @@
   <si>
     <t>Coin</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션_동관_50045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션_동관_50046</t>
+  </si>
+  <si>
+    <t>미션_동관_50047</t>
+  </si>
+  <si>
+    <t>미션_동관_50048</t>
+  </si>
+  <si>
+    <t>미션_동관_50049</t>
+  </si>
+  <si>
+    <t>미션_동관_50050</t>
+  </si>
+  <si>
+    <t>미션_동관_50051</t>
+  </si>
+  <si>
+    <t>미션_동관_50052</t>
+  </si>
+  <si>
+    <t>mission_b_50045</t>
+  </si>
+  <si>
+    <t>mission_b_50046</t>
+  </si>
+  <si>
+    <t>mission_b_50047</t>
+  </si>
+  <si>
+    <t>mission_b_50048</t>
+  </si>
+  <si>
+    <t>mission_b_50049</t>
+  </si>
+  <si>
+    <t>mission_b_50050</t>
+  </si>
+  <si>
+    <t>mission_b_50051</t>
+  </si>
+  <si>
+    <t>mission_b_50052</t>
   </si>
 </sst>
 </file>
@@ -3968,7 +4017,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -5038,6 +5087,190 @@
         <v>68</v>
       </c>
     </row>
+    <row r="47" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="32">
+        <v>70045</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="35">
+        <v>1</v>
+      </c>
+      <c r="F47" s="32">
+        <v>50045</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="32">
+        <v>70046</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="35">
+        <v>1</v>
+      </c>
+      <c r="F48" s="32">
+        <v>50046</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="32">
+        <v>70047</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="35">
+        <v>1</v>
+      </c>
+      <c r="F49" s="32">
+        <v>50047</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="32">
+        <v>70048</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="35">
+        <v>1</v>
+      </c>
+      <c r="F50" s="32">
+        <v>50048</v>
+      </c>
+      <c r="G50" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="32">
+        <v>70049</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="35">
+        <v>31000</v>
+      </c>
+      <c r="F51" s="32">
+        <v>50049</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="32">
+        <v>70050</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="35">
+        <v>32000</v>
+      </c>
+      <c r="F52" s="32">
+        <v>50050</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="32">
+        <v>70051</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" s="35">
+        <v>34000</v>
+      </c>
+      <c r="F53" s="32">
+        <v>50051</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="32">
+        <v>70052</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" s="35">
+        <v>33000</v>
+      </c>
+      <c r="F54" s="32">
+        <v>50052</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5049,13 +5282,13 @@
           <x14:formula1>
             <xm:f>Type!$A$3:$A$118</xm:f>
           </x14:formula1>
-          <xm:sqref>D47:D1048576</xm:sqref>
+          <xm:sqref>D55:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Type!$A$2:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D46</xm:sqref>
+          <xm:sqref>D2:D54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Mission.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Mission.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -203,59 +203,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mission_b_50000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mission_b_50001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mission_b_50002</t>
-  </si>
-  <si>
-    <t>mission_b_50003</t>
-  </si>
-  <si>
-    <t>mission_b_50004</t>
-  </si>
-  <si>
-    <t>mission_b_50005</t>
-  </si>
-  <si>
-    <t>mission_b_50006</t>
-  </si>
-  <si>
-    <t>mission_b_50007</t>
-  </si>
-  <si>
     <t>mission_b_50008</t>
-  </si>
-  <si>
-    <t>미션_동관_50000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션_동관_50001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션_동관_50002</t>
-  </si>
-  <si>
-    <t>미션_동관_50003</t>
-  </si>
-  <si>
-    <t>미션_동관_50004</t>
-  </si>
-  <si>
-    <t>미션_동관_50005</t>
-  </si>
-  <si>
-    <t>미션_동관_50006</t>
-  </si>
-  <si>
-    <t>미션_동관_50007</t>
   </si>
   <si>
     <t>미션_동관_50008</t>
@@ -289,10 +237,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Coin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Bronze</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,48 +245,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>미션_동관_50009</t>
-  </si>
-  <si>
-    <t>mission_b_50009</t>
-  </si>
-  <si>
-    <t>미션_동관_50010</t>
-  </si>
-  <si>
-    <t>mission_b_50010</t>
-  </si>
-  <si>
-    <t>미션_동관_50011</t>
-  </si>
-  <si>
-    <t>mission_b_50011</t>
-  </si>
-  <si>
-    <t>미션_동관_50012</t>
-  </si>
-  <si>
-    <t>mission_b_50012</t>
-  </si>
-  <si>
     <t>미션_동관_50013</t>
   </si>
   <si>
     <t>mission_b_50013</t>
   </si>
   <si>
-    <t>미션_동관_50014</t>
-  </si>
-  <si>
-    <t>mission_b_50014</t>
-  </si>
-  <si>
-    <t>미션_동관_50015</t>
-  </si>
-  <si>
-    <t>mission_b_50015</t>
-  </si>
-  <si>
     <t>미션_동관_50016</t>
   </si>
   <si>
@@ -379,12 +287,6 @@
     <t>mission_b_50021</t>
   </si>
   <si>
-    <t>미션_동관_50022</t>
-  </si>
-  <si>
-    <t>mission_b_50022</t>
-  </si>
-  <si>
     <t>미션_동관_50023</t>
   </si>
   <si>
@@ -397,152 +299,36 @@
     <t>mission_b_50024</t>
   </si>
   <si>
-    <t>미션_동관_50025</t>
-  </si>
-  <si>
-    <t>mission_b_50025</t>
-  </si>
-  <si>
     <t>미션_동관_50026</t>
   </si>
   <si>
     <t>mission_b_50026</t>
   </si>
   <si>
-    <t>미션_동관_50027</t>
-  </si>
-  <si>
-    <t>mission_b_50027</t>
-  </si>
-  <si>
-    <t>미션_동관_50028</t>
-  </si>
-  <si>
-    <t>mission_b_50028</t>
-  </si>
-  <si>
     <t>미션_동관_50029</t>
   </si>
   <si>
     <t>mission_b_50029</t>
   </si>
   <si>
-    <t>미션_동관_50030</t>
-  </si>
-  <si>
-    <t>mission_b_50030</t>
-  </si>
-  <si>
-    <t>미션_동관_50031</t>
-  </si>
-  <si>
-    <t>mission_b_50031</t>
-  </si>
-  <si>
-    <t>미션_동관_50032</t>
-  </si>
-  <si>
-    <t>mission_b_50032</t>
-  </si>
-  <si>
-    <t>미션_동관_50033</t>
-  </si>
-  <si>
-    <t>mission_b_50033</t>
-  </si>
-  <si>
-    <t>미션_동관_50034</t>
-  </si>
-  <si>
-    <t>mission_b_50034</t>
-  </si>
-  <si>
-    <t>미션_동관_50035</t>
-  </si>
-  <si>
-    <t>mission_b_50035</t>
-  </si>
-  <si>
-    <t>미션_동관_50036</t>
-  </si>
-  <si>
-    <t>mission_b_50036</t>
-  </si>
-  <si>
     <t>미션_동관_50037</t>
   </si>
   <si>
     <t>mission_b_50037</t>
   </si>
   <si>
-    <t>미션_동관_50038</t>
-  </si>
-  <si>
-    <t>mission_b_50038</t>
-  </si>
-  <si>
-    <t>미션_동관_50039</t>
-  </si>
-  <si>
-    <t>mission_b_50039</t>
-  </si>
-  <si>
-    <t>미션_동관_50040</t>
-  </si>
-  <si>
-    <t>mission_b_50040</t>
-  </si>
-  <si>
-    <t>미션_동관_50041</t>
-  </si>
-  <si>
-    <t>mission_b_50041</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>미션_동관_50042</t>
-  </si>
-  <si>
-    <t>mission_b_50042</t>
-  </si>
-  <si>
-    <t>미션_동관_50043</t>
-  </si>
-  <si>
-    <t>mission_b_50043</t>
-  </si>
-  <si>
     <t>미션_동관_50044</t>
   </si>
   <si>
     <t>mission_b_50044</t>
   </si>
   <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>Coin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션_동관_50045</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션_동관_50046</t>
-  </si>
-  <si>
-    <t>미션_동관_50047</t>
-  </si>
-  <si>
-    <t>미션_동관_50048</t>
-  </si>
-  <si>
     <t>미션_동관_50049</t>
   </si>
   <si>
@@ -553,18 +339,6 @@
   </si>
   <si>
     <t>미션_동관_50052</t>
-  </si>
-  <si>
-    <t>mission_b_50045</t>
-  </si>
-  <si>
-    <t>mission_b_50046</t>
-  </si>
-  <si>
-    <t>mission_b_50047</t>
-  </si>
-  <si>
-    <t>mission_b_50048</t>
   </si>
   <si>
     <t>mission_b_50049</t>
@@ -3332,7 +3106,7 @@
         <v>99999999</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -4017,7 +3791,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -4057,206 +3831,206 @@
         <v>70000</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>46</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E2" s="35">
-        <v>1</v>
+        <v>35001</v>
       </c>
       <c r="F2" s="35">
-        <v>50000</v>
+        <v>50008</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
         <v>70001</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E3" s="35">
-        <v>1</v>
-      </c>
-      <c r="F3" s="35">
-        <v>50001</v>
+        <v>34000</v>
+      </c>
+      <c r="F3" s="32">
+        <v>50013</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
         <v>70002</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E4" s="35">
-        <v>1</v>
-      </c>
-      <c r="F4" s="35">
-        <v>50002</v>
+        <v>30000</v>
+      </c>
+      <c r="F4" s="32">
+        <v>50016</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="32">
         <v>70003</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E5" s="35">
-        <v>1</v>
-      </c>
-      <c r="F5" s="35">
-        <v>50003</v>
+        <v>35002</v>
+      </c>
+      <c r="F5" s="32">
+        <v>50017</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
         <v>70004</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E6" s="35">
-        <v>1</v>
-      </c>
-      <c r="F6" s="35">
-        <v>50004</v>
+        <v>5000</v>
+      </c>
+      <c r="F6" s="32">
+        <v>50018</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="32">
         <v>70005</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E7" s="35">
-        <v>1</v>
-      </c>
-      <c r="F7" s="35">
-        <v>50005</v>
+        <v>39000</v>
+      </c>
+      <c r="F7" s="32">
+        <v>50019</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="32">
         <v>70006</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C8" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="35">
+        <v>3</v>
+      </c>
+      <c r="F8" s="32">
+        <v>50020</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="35">
-        <v>1</v>
-      </c>
-      <c r="F8" s="35">
-        <v>50006</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="32">
         <v>70007</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E9" s="35">
-        <v>1</v>
-      </c>
-      <c r="F9" s="35">
-        <v>50007</v>
+        <v>5000</v>
+      </c>
+      <c r="F9" s="32">
+        <v>50021</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="32">
         <v>70008</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E10" s="35">
-        <v>35001</v>
-      </c>
-      <c r="F10" s="35">
-        <v>50008</v>
+        <v>39001</v>
+      </c>
+      <c r="F10" s="32">
+        <v>50023</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -4264,22 +4038,22 @@
         <v>70009</v>
       </c>
       <c r="B11" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="35" t="s">
-        <v>75</v>
-      </c>
       <c r="D11" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E11" s="35">
-        <v>1</v>
+        <v>32003</v>
       </c>
       <c r="F11" s="32">
-        <v>50009</v>
+        <v>50024</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4287,22 +4061,22 @@
         <v>70010</v>
       </c>
       <c r="B12" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>77</v>
-      </c>
       <c r="D12" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E12" s="35">
-        <v>1</v>
+        <v>33003</v>
       </c>
       <c r="F12" s="32">
-        <v>50010</v>
+        <v>50026</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4310,22 +4084,22 @@
         <v>70011</v>
       </c>
       <c r="B13" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>79</v>
-      </c>
       <c r="D13" s="35" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E13" s="35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" s="32">
-        <v>50011</v>
+        <v>50029</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -4333,22 +4107,22 @@
         <v>70012</v>
       </c>
       <c r="B14" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>81</v>
-      </c>
       <c r="D14" s="35" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E14" s="35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" s="32">
-        <v>50012</v>
+        <v>50037</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -4356,48 +4130,48 @@
         <v>70013</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E15" s="35">
-        <v>34000</v>
+        <v>35003</v>
       </c>
       <c r="F15" s="32">
-        <v>50013</v>
+        <v>50044</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="32">
         <v>70014</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E16" s="35">
-        <v>1</v>
+        <v>31000</v>
       </c>
       <c r="F16" s="32">
-        <v>50014</v>
+        <v>50049</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="32">
         <v>70015</v>
       </c>
@@ -4405,871 +4179,69 @@
         <v>86</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E17" s="35">
-        <v>1</v>
+        <v>32000</v>
       </c>
       <c r="F17" s="32">
-        <v>50015</v>
+        <v>50050</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="32">
         <v>70016</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E18" s="35">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="F18" s="32">
-        <v>50016</v>
+        <v>50051</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32">
         <v>70017</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E19" s="35">
-        <v>35002</v>
+        <v>33000</v>
       </c>
       <c r="F19" s="32">
-        <v>50017</v>
+        <v>50052</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="32">
-        <v>70018</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="35">
-        <v>5000</v>
-      </c>
-      <c r="F20" s="32">
-        <v>50018</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="32">
-        <v>70019</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="35">
-        <v>39000</v>
-      </c>
-      <c r="F21" s="32">
-        <v>50019</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="32">
-        <v>70020</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="35">
-        <v>3</v>
-      </c>
-      <c r="F22" s="32">
-        <v>50020</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="32">
-        <v>70021</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="35">
-        <v>5000</v>
-      </c>
-      <c r="F23" s="32">
-        <v>50021</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="32">
-        <v>70022</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="35">
-        <v>1</v>
-      </c>
-      <c r="F24" s="32">
-        <v>50022</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="32">
-        <v>70023</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" s="35">
-        <v>39001</v>
-      </c>
-      <c r="F25" s="32">
-        <v>50023</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="32">
-        <v>70024</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="35">
-        <v>32003</v>
-      </c>
-      <c r="F26" s="32">
-        <v>50024</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="32">
-        <v>70025</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="35">
-        <v>1</v>
-      </c>
-      <c r="F27" s="32">
-        <v>50025</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="32">
-        <v>70026</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" s="35">
-        <v>33003</v>
-      </c>
-      <c r="F28" s="32">
-        <v>50026</v>
-      </c>
-      <c r="G28" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="32">
-        <v>70027</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="35">
-        <v>1</v>
-      </c>
-      <c r="F29" s="32">
-        <v>50027</v>
-      </c>
-      <c r="G29" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="32">
-        <v>70028</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="35">
-        <v>1</v>
-      </c>
-      <c r="F30" s="32">
-        <v>50028</v>
-      </c>
-      <c r="G30" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="32">
-        <v>70029</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="35">
-        <v>1</v>
-      </c>
-      <c r="F31" s="32">
-        <v>50029</v>
-      </c>
-      <c r="G31" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="32">
-        <v>70030</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="35">
-        <v>1</v>
-      </c>
-      <c r="F32" s="32">
-        <v>50030</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="32">
-        <v>70031</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="35">
-        <v>1</v>
-      </c>
-      <c r="F33" s="32">
-        <v>50031</v>
-      </c>
-      <c r="G33" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="32">
-        <v>70032</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="35">
-        <v>1</v>
-      </c>
-      <c r="F34" s="32">
-        <v>50032</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="32">
-        <v>70033</v>
-      </c>
-      <c r="B35" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E35" s="35">
-        <v>1</v>
-      </c>
-      <c r="F35" s="32">
-        <v>50033</v>
-      </c>
-      <c r="G35" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="32">
-        <v>70034</v>
-      </c>
-      <c r="B36" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="35">
-        <v>1</v>
-      </c>
-      <c r="F36" s="32">
-        <v>50034</v>
-      </c>
-      <c r="G36" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="32">
-        <v>70035</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" s="35">
-        <v>1</v>
-      </c>
-      <c r="F37" s="32">
-        <v>50035</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="32">
-        <v>70036</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="35">
-        <v>1</v>
-      </c>
-      <c r="F38" s="32">
-        <v>50036</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="32">
-        <v>70037</v>
-      </c>
-      <c r="B39" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C39" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E39" s="35">
-        <v>1</v>
-      </c>
-      <c r="F39" s="32">
-        <v>50037</v>
-      </c>
-      <c r="G39" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="32">
-        <v>70038</v>
-      </c>
-      <c r="B40" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" s="35">
-        <v>1</v>
-      </c>
-      <c r="F40" s="32">
-        <v>50038</v>
-      </c>
-      <c r="G40" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="32">
-        <v>70039</v>
-      </c>
-      <c r="B41" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="35">
-        <v>1</v>
-      </c>
-      <c r="F41" s="32">
-        <v>50039</v>
-      </c>
-      <c r="G41" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="32">
-        <v>70040</v>
-      </c>
-      <c r="B42" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" s="35">
-        <v>1</v>
-      </c>
-      <c r="F42" s="32">
-        <v>50040</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="32">
-        <v>70041</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="35">
-        <v>1</v>
-      </c>
-      <c r="F43" s="32">
-        <v>50041</v>
-      </c>
-      <c r="G43" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="32">
-        <v>70042</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" s="35">
-        <v>1</v>
-      </c>
-      <c r="F44" s="32">
-        <v>50042</v>
-      </c>
-      <c r="G44" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="32">
-        <v>70043</v>
-      </c>
-      <c r="B45" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C45" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45" s="35">
-        <v>1</v>
-      </c>
-      <c r="F45" s="32">
-        <v>50043</v>
-      </c>
-      <c r="G45" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="32">
-        <v>70044</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="D46" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" s="35">
-        <v>35003</v>
-      </c>
-      <c r="F46" s="32">
-        <v>50044</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="32">
-        <v>70045</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D47" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="35">
-        <v>1</v>
-      </c>
-      <c r="F47" s="32">
-        <v>50045</v>
-      </c>
-      <c r="G47" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="32">
-        <v>70046</v>
-      </c>
-      <c r="B48" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="D48" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="35">
-        <v>1</v>
-      </c>
-      <c r="F48" s="32">
-        <v>50046</v>
-      </c>
-      <c r="G48" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="32">
-        <v>70047</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D49" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="35">
-        <v>1</v>
-      </c>
-      <c r="F49" s="32">
-        <v>50047</v>
-      </c>
-      <c r="G49" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="32">
-        <v>70048</v>
-      </c>
-      <c r="B50" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="35">
-        <v>1</v>
-      </c>
-      <c r="F50" s="32">
-        <v>50048</v>
-      </c>
-      <c r="G50" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="32">
-        <v>70049</v>
-      </c>
-      <c r="B51" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="C51" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="35">
-        <v>31000</v>
-      </c>
-      <c r="F51" s="32">
-        <v>50049</v>
-      </c>
-      <c r="G51" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="32">
-        <v>70050</v>
-      </c>
-      <c r="B52" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C52" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="35">
-        <v>32000</v>
-      </c>
-      <c r="F52" s="32">
-        <v>50050</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="32">
-        <v>70051</v>
-      </c>
-      <c r="B53" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E53" s="35">
-        <v>34000</v>
-      </c>
-      <c r="F53" s="32">
-        <v>50051</v>
-      </c>
-      <c r="G53" s="35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="32">
-        <v>70052</v>
-      </c>
-      <c r="B54" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="D54" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E54" s="35">
-        <v>33000</v>
-      </c>
-      <c r="F54" s="32">
-        <v>50052</v>
-      </c>
-      <c r="G54" s="35" t="s">
-        <v>72</v>
-      </c>
+      <c r="E24" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5282,13 +4254,13 @@
           <x14:formula1>
             <xm:f>Type!$A$3:$A$118</xm:f>
           </x14:formula1>
-          <xm:sqref>D55:D1048576</xm:sqref>
+          <xm:sqref>D20:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Type!$A$2:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D54</xm:sqref>
+          <xm:sqref>D2:D19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5310,7 +4282,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -5351,10 +4323,10 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -5373,10 +4345,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -5395,10 +4367,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>

--- a/30_table/01_테스트버전/Table_Data_Mission.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Mission.xlsx
@@ -4001,7 +4001,7 @@
         <v>82</v>
       </c>
       <c r="E9" s="35">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="32">
         <v>50021</v>

--- a/30_table/01_테스트버전/Table_Data_Mission.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Mission.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="88">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -263,12 +263,6 @@
     <t>mission_b_50017</t>
   </si>
   <si>
-    <t>미션_동관_50018</t>
-  </si>
-  <si>
-    <t>mission_b_50018</t>
-  </si>
-  <si>
     <t>미션_동관_50019</t>
   </si>
   <si>
@@ -281,12 +275,6 @@
     <t>mission_b_50020</t>
   </si>
   <si>
-    <t>미션_동관_50021</t>
-  </si>
-  <si>
-    <t>mission_b_50021</t>
-  </si>
-  <si>
     <t>미션_동관_50023</t>
   </si>
   <si>
@@ -318,9 +306,6 @@
   </si>
   <si>
     <t>Item</t>
-  </si>
-  <si>
-    <t>Gold</t>
   </si>
   <si>
     <t>미션_동관_50044</t>
@@ -3791,7 +3776,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -3837,7 +3822,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E2" s="35">
         <v>35001</v>
@@ -3860,7 +3845,7 @@
         <v>58</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" s="35">
         <v>34000</v>
@@ -3883,7 +3868,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4" s="35">
         <v>30000</v>
@@ -3929,13 +3914,13 @@
         <v>64</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E6" s="35">
-        <v>5000</v>
+        <v>39000</v>
       </c>
       <c r="F6" s="32">
-        <v>50018</v>
+        <v>50019</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>52</v>
@@ -3952,13 +3937,13 @@
         <v>66</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E7" s="35">
-        <v>39000</v>
+        <v>3</v>
       </c>
       <c r="F7" s="32">
-        <v>50019</v>
+        <v>50020</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>52</v>
@@ -3975,13 +3960,13 @@
         <v>68</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E8" s="35">
-        <v>3</v>
+        <v>39001</v>
       </c>
       <c r="F8" s="32">
-        <v>50020</v>
+        <v>50023</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>52</v>
@@ -3998,13 +3983,13 @@
         <v>70</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E9" s="35">
-        <v>10000</v>
+        <v>32003</v>
       </c>
       <c r="F9" s="32">
-        <v>50021</v>
+        <v>50024</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>52</v>
@@ -4021,13 +4006,13 @@
         <v>72</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E10" s="35">
-        <v>39001</v>
+        <v>33003</v>
       </c>
       <c r="F10" s="32">
-        <v>50023</v>
+        <v>50026</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>52</v>
@@ -4044,13 +4029,13 @@
         <v>74</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E11" s="35">
-        <v>32003</v>
+        <v>5</v>
       </c>
       <c r="F11" s="32">
-        <v>50024</v>
+        <v>50029</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>52</v>
@@ -4067,13 +4052,13 @@
         <v>76</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E12" s="35">
-        <v>33003</v>
+        <v>5</v>
       </c>
       <c r="F12" s="32">
-        <v>50026</v>
+        <v>50037</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>52</v>
@@ -4084,68 +4069,68 @@
         <v>70011</v>
       </c>
       <c r="B13" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>49</v>
-      </c>
       <c r="E13" s="35">
-        <v>5</v>
+        <v>35003</v>
       </c>
       <c r="F13" s="32">
-        <v>50029</v>
+        <v>50044</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32">
         <v>70012</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E14" s="35">
-        <v>5</v>
+        <v>31000</v>
       </c>
       <c r="F14" s="32">
-        <v>50037</v>
+        <v>50049</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32">
         <v>70013</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E15" s="35">
-        <v>35003</v>
+        <v>32000</v>
       </c>
       <c r="F15" s="32">
-        <v>50044</v>
+        <v>50050</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
@@ -4153,19 +4138,19 @@
         <v>70014</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E16" s="35">
-        <v>31000</v>
+        <v>34000</v>
       </c>
       <c r="F16" s="32">
-        <v>50049</v>
+        <v>50051</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>55</v>
@@ -4176,72 +4161,26 @@
         <v>70015</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E17" s="35">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="F17" s="32">
-        <v>50050</v>
+        <v>50052</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32">
-        <v>70016</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="35">
-        <v>34000</v>
-      </c>
-      <c r="F18" s="32">
-        <v>50051</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32">
-        <v>70017</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="35">
-        <v>33000</v>
-      </c>
-      <c r="F19" s="32">
-        <v>50052</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E24" s="32"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E22" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4254,13 +4193,13 @@
           <x14:formula1>
             <xm:f>Type!$A$3:$A$118</xm:f>
           </x14:formula1>
-          <xm:sqref>D20:D1048576</xm:sqref>
+          <xm:sqref>D18:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Type!$A$2:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D19</xm:sqref>
+          <xm:sqref>D2:D17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
